--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 20:34</t>
+    <t xml:space="preserve">2026-08-02 20:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 20:07</t>
+    <t xml:space="preserve">2026-08-05 11:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 11:04</t>
+    <t xml:space="preserve">2026-08-16 10:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 10:11</t>
+    <t xml:space="preserve">2026-08-19 14:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:36</t>
+    <t xml:space="preserve">2026-08-28 12:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 12:33</t>
+    <t xml:space="preserve">2026-09-06 17:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
